--- a/data/trans_orig/P21D1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35585</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63904</t>
+          <t>62360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36236</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>57509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76963</t>
+          <t>76330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112644</t>
+          <t>111534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155880</t>
+          <t>157738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185035</t>
+          <t>185405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154626</t>
+          <t>154995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>177939</t>
+          <t>177906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>320005</t>
+          <t>321086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356978</t>
+          <t>358581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26910</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>48492</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>24128</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43155</t>
+          <t>42703</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55235</t>
+          <t>56262</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84311</t>
+          <t>84488</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130641</t>
+          <t>130945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153236</t>
+          <t>153509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129075</t>
+          <t>128952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149545</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>266390</t>
+          <t>267589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297081</t>
+          <t>296238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>38912</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>106202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110804</t>
+          <t>110185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>375502</t>
+          <t>375501</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>309364</t>
+          <t>307328</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>405310</t>
+          <t>405186</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56478</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67946</t>
+          <t>68387</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>374895</t>
+          <t>375387</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>477280</t>
+          <t>480101</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2973</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104441</t>
+          <t>104063</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145233</t>
+          <t>145417</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43560</t>
+          <t>42683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67223</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>154878</t>
+          <t>153344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>203840</t>
+          <t>202440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>294623</t>
+          <t>296473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>337785</t>
+          <t>338926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261429</t>
+          <t>263129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>287810</t>
+          <t>287897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>566552</t>
+          <t>569328</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615973</t>
+          <t>618780</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,8%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33291</t>
+          <t>36627</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -2776,97 +2776,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1765</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3507</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3835</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3983</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3485</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39080</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67067</t>
+          <t>66845</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56038</t>
+          <t>55031</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>258266</t>
+          <t>234400</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108243</t>
+          <t>108240</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>299343</t>
+          <t>333905</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147361</t>
+          <t>148360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178294</t>
+          <t>178576</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156936</t>
+          <t>178029</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>353793</t>
+          <t>354366</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>334160</t>
+          <t>304709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>518259</t>
+          <t>518768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24372</t>
+          <t>26301</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3345,97 +3345,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1719</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>3537</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>4079</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>3738</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27738</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>62386</t>
+          <t>64829</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>56952</t>
+          <t>55945</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>89705</t>
+          <t>87904</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>93320</t>
+          <t>91786</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>142191</t>
+          <t>143272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60941</t>
+          <t>58498</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>95941</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>224653</t>
+          <t>225625</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>257930</t>
+          <t>257815</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>295426</t>
+          <t>294112</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>344929</t>
+          <t>344376</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3914,97 +3914,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>4140</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1566</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>207281</t>
+          <t>205373</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>422084</t>
+          <t>420009</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>268484</t>
+          <t>270845</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>536197</t>
+          <t>559550</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>545356</t>
+          <t>534537</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>841252</t>
+          <t>843522</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1170520</t>
+          <t>1170137</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1405755</t>
+          <t>1395561</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>983606</t>
+          <t>951757</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1246537</t>
+          <t>1244648</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2285745</t>
+          <t>2278894</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2579119</t>
+          <t>2589639</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>45582</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22934</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>44190</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>41457</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>80761</t>
+          <t>80087</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4483,82 +4483,82 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>2189</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5149</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>4673</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">

--- a/data/trans_orig/P21D1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46636</t>
+          <t>50914</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>66965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46068</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35203</t>
+          <t>36944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57509</t>
+          <t>61941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>92704</t>
+          <t>100447</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76330</t>
+          <t>83544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111534</t>
+          <t>120966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>173408</t>
+          <t>187136</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157738</t>
+          <t>170756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185405</t>
+          <t>201764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>166952</t>
+          <t>180203</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154995</t>
+          <t>166847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>177906</t>
+          <t>193234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>340360</t>
+          <t>367339</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>321086</t>
+          <t>347182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358581</t>
+          <t>384954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19558</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>42303</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>31595</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48492</t>
+          <t>55658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,27 +1329,27 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>27282</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42703</t>
+          <t>47177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69689</t>
+          <t>78799</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56262</t>
+          <t>65055</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84488</t>
+          <t>96978</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>142981</t>
+          <t>152523</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130945</t>
+          <t>139142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153509</t>
+          <t>163333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>139676</t>
+          <t>154417</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128952</t>
+          <t>142745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150057</t>
+          <t>164261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>282656</t>
+          <t>306940</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267589</t>
+          <t>288784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>296238</t>
+          <t>322321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,22 +1555,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38912</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106202</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>20617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51931</t>
+          <t>56248</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>44462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110185</t>
+          <t>73173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>375501</t>
+          <t>145732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>307328</t>
+          <t>131828</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>405186</t>
+          <t>157199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62676</t>
+          <t>69068</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56452</t>
+          <t>62471</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68387</t>
+          <t>74675</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>438178</t>
+          <t>214800</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>375387</t>
+          <t>197556</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>480101</t>
+          <t>227179</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>124628</t>
+          <t>142736</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104063</t>
+          <t>118409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145417</t>
+          <t>165415</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53487</t>
+          <t>58610</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42683</t>
+          <t>46164</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>72484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178115</t>
+          <t>201345</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>153344</t>
+          <t>177946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202440</t>
+          <t>230269</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>317023</t>
+          <t>354220</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296473</t>
+          <t>331969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>338926</t>
+          <t>378475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>276576</t>
+          <t>318484</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263129</t>
+          <t>304619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>287897</t>
+          <t>330884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>593598</t>
+          <t>672704</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569328</t>
+          <t>642772</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>618780</t>
+          <t>696908</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>26215</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>24345</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36627</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>52781</t>
+          <t>80246</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>63521</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66845</t>
+          <t>99732</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119048</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55031</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>234400</t>
+          <t>77985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>171829</t>
+          <t>143116</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108240</t>
+          <t>121199</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>333905</t>
+          <t>168565</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>163518</t>
+          <t>179284</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>148360</t>
+          <t>161069</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>197096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>291530</t>
+          <t>319872</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>178029</t>
+          <t>305128</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>354366</t>
+          <t>332158</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>455048</t>
+          <t>499157</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>304709</t>
+          <t>473644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>518768</t>
+          <t>520760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26301</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>43719</t>
+          <t>48002</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27738</t>
+          <t>34157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>64829</t>
+          <t>65654</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>70920</t>
+          <t>81472</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55945</t>
+          <t>64596</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>87904</t>
+          <t>99118</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>114640</t>
+          <t>129474</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>91786</t>
+          <t>105883</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>143272</t>
+          <t>156557</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>79608</t>
+          <t>69435</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>58498</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>83280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>243503</t>
+          <t>268960</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>225625</t>
+          <t>250919</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>257815</t>
+          <t>286194</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>323112</t>
+          <t>338396</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>294112</t>
+          <t>312546</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>344376</t>
+          <t>362522</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>343453</t>
+          <t>406302</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>205373</t>
+          <t>366583</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>420009</t>
+          <t>449343</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>335456</t>
+          <t>303127</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>270845</t>
+          <t>274129</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>559550</t>
+          <t>333491</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>678908</t>
+          <t>709429</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>534537</t>
+          <t>655593</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>843522</t>
+          <t>762618</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1252040</t>
+          <t>1088333</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1170137</t>
+          <t>1042927</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1395561</t>
+          <t>1130948</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1180913</t>
+          <t>1311005</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>951757</t>
+          <t>1279631</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1244648</t>
+          <t>1340106</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2432954</t>
+          <t>2399337</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2278894</t>
+          <t>2344079</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2589639</t>
+          <t>2454606</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>77,31%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>45582</t>
+          <t>47694</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>45257</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>59588</t>
+          <t>64911</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>42170</t>
+          <t>50538</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>80087</t>
+          <t>87819</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
